--- a/Assets/ExcelSource/Localization.xlsx
+++ b/Assets/ExcelSource/Localization.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Text" sheetId="1" r:id="R106cf7a7dee041f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Text" sheetId="1" r:id="R9d721575b7fc4338"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -57474,6 +57474,1455 @@
         <x:v>Bonificación de runa {0}</x:v>
       </x:c>
     </x:row>
+    <x:row r="1481">
+      <x:c r="A1481" t="str">
+        <x:v>data.skill_master.s_core_61.name</x:v>
+      </x:c>
+      <x:c r="B1481" t="str">
+        <x:v>41387432259100789</x:v>
+      </x:c>
+      <x:c r="C1481" t="str">
+        <x:v>위압</x:v>
+      </x:c>
+      <x:c r="D1481" t="str">
+        <x:v>Overbearing</x:v>
+      </x:c>
+      <x:c r="E1481" t="str">
+        <x:v>霸道</x:v>
+      </x:c>
+      <x:c r="F1481" t="str">
+        <x:v>威圧</x:v>
+      </x:c>
+      <x:c r="G1481" t="str">
+        <x:v>Dominante</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1482">
+      <x:c r="A1482" t="str">
+        <x:v>data.skill_master.s_core_61.tooltip</x:v>
+      </x:c>
+      <x:c r="B1482" t="str">
+        <x:v>41387432259100790</x:v>
+      </x:c>
+      <x:c r="C1482" t="str">
+        <x:v>상대의 기세를 억눌러 약화 1을 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1482" t="str">
+        <x:v>Suppresses the opponent's momentum and inflicts 1 weakening.</x:v>
+      </x:c>
+      <x:c r="E1482" t="str">
+        <x:v>压制对手的气势并造成1点削弱。</x:v>
+      </x:c>
+      <x:c r="F1482" t="str">
+        <x:v>相手の勢いを抑えて弱体化1を与えます。</x:v>
+      </x:c>
+      <x:c r="G1482" t="str">
+        <x:v>Suprime el impulso del oponente e inflige 1 debilitamiento.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1483">
+      <x:c r="A1483" t="str">
+        <x:v>data.skill_master.s_core_61.details</x:v>
+      </x:c>
+      <x:c r="B1483" t="str">
+        <x:v>41387432259100791</x:v>
+      </x:c>
+      <x:c r="C1483" t="str">
+        <x:v>약화 1을 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1483" t="str">
+        <x:v>Grants Weakness 1.</x:v>
+      </x:c>
+      <x:c r="E1483" t="str">
+        <x:v>授予弱点 1。</x:v>
+      </x:c>
+      <x:c r="F1483" t="str">
+        <x:v>弱さ 1 を与えます。</x:v>
+      </x:c>
+      <x:c r="G1483" t="str">
+        <x:v>Otorga la debilidad 1.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1484">
+      <x:c r="A1484" t="str">
+        <x:v>data.skill_master.s_core_62.name</x:v>
+      </x:c>
+      <x:c r="B1484" t="str">
+        <x:v>41387432259100792</x:v>
+      </x:c>
+      <x:c r="C1484" t="str">
+        <x:v>위압+</x:v>
+      </x:c>
+      <x:c r="D1484" t="str">
+        <x:v>Intimidating+</x:v>
+      </x:c>
+      <x:c r="E1484" t="str">
+        <x:v>恐吓+</x:v>
+      </x:c>
+      <x:c r="F1484" t="str">
+        <x:v>威圧+</x:v>
+      </x:c>
+      <x:c r="G1484" t="str">
+        <x:v>Intimidante+</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1485">
+      <x:c r="A1485" t="str">
+        <x:v>data.skill_master.s_core_62.tooltip</x:v>
+      </x:c>
+      <x:c r="B1485" t="str">
+        <x:v>41387432259100793</x:v>
+      </x:c>
+      <x:c r="C1485" t="str">
+        <x:v>상대의 기세를 억눌러 약화 1을 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1485" t="str">
+        <x:v>Suppresses the opponent's momentum and inflicts 1 weakening.</x:v>
+      </x:c>
+      <x:c r="E1485" t="str">
+        <x:v>压制对手的气势并造成1点削弱。</x:v>
+      </x:c>
+      <x:c r="F1485" t="str">
+        <x:v>相手の勢いを抑えて弱体化1を与えます。</x:v>
+      </x:c>
+      <x:c r="G1485" t="str">
+        <x:v>Suprime el impulso del oponente e inflige 1 debilitamiento.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1486">
+      <x:c r="A1486" t="str">
+        <x:v>data.skill_master.s_core_62.details</x:v>
+      </x:c>
+      <x:c r="B1486" t="str">
+        <x:v>41387432259100794</x:v>
+      </x:c>
+      <x:c r="C1486" t="str">
+        <x:v>약화 1을 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1486" t="str">
+        <x:v>Grants Weakness 1.</x:v>
+      </x:c>
+      <x:c r="E1486" t="str">
+        <x:v>授予弱点 1。</x:v>
+      </x:c>
+      <x:c r="F1486" t="str">
+        <x:v>弱さ 1 を与えます。</x:v>
+      </x:c>
+      <x:c r="G1486" t="str">
+        <x:v>Otorga la debilidad 1.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1487">
+      <x:c r="A1487" t="str">
+        <x:v>data.skill_master.s_core_63.name</x:v>
+      </x:c>
+      <x:c r="B1487" t="str">
+        <x:v>41387432259100795</x:v>
+      </x:c>
+      <x:c r="C1487" t="str">
+        <x:v>공격태세</x:v>
+      </x:c>
+      <x:c r="D1487" t="str">
+        <x:v>Attack stance</x:v>
+      </x:c>
+      <x:c r="E1487" t="str">
+        <x:v>攻击姿态</x:v>
+      </x:c>
+      <x:c r="F1487" t="str">
+        <x:v>攻撃態勢</x:v>
+      </x:c>
+      <x:c r="G1487" t="str">
+        <x:v>Postura de ataque</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1488">
+      <x:c r="A1488" t="str">
+        <x:v>data.skill_master.s_core_63.tooltip</x:v>
+      </x:c>
+      <x:c r="B1488" t="str">
+        <x:v>41387432259100796</x:v>
+      </x:c>
+      <x:c r="C1488" t="str">
+        <x:v>자신과 아군에게 증폭 1을 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1488" t="str">
+        <x:v>Gives you and your allies Amplification 1.</x:v>
+      </x:c>
+      <x:c r="E1488" t="str">
+        <x:v>为你和你的盟友提供1倍增幅。</x:v>
+      </x:c>
+      <x:c r="F1488" t="str">
+        <x:v>自分と味方に増幅1を与えます。</x:v>
+      </x:c>
+      <x:c r="G1488" t="str">
+        <x:v>Te da a ti y a tus aliados Amplificación 1.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1489">
+      <x:c r="A1489" t="str">
+        <x:v>data.skill_master.s_core_63.details</x:v>
+      </x:c>
+      <x:c r="B1489" t="str">
+        <x:v>41387432259100797</x:v>
+      </x:c>
+      <x:c r="C1489" t="str">
+        <x:v>자신과 아군에게 증폭 1을 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1489" t="str">
+        <x:v>Gives you and your allies Amplification 1.</x:v>
+      </x:c>
+      <x:c r="E1489" t="str">
+        <x:v>为你和你的盟友提供1倍增幅。</x:v>
+      </x:c>
+      <x:c r="F1489" t="str">
+        <x:v>自分と味方に増幅1を与えます。</x:v>
+      </x:c>
+      <x:c r="G1489" t="str">
+        <x:v>Te da a ti y a tus aliados Amplificación 1.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1490">
+      <x:c r="A1490" t="str">
+        <x:v>data.skill_master.s_core_64.name</x:v>
+      </x:c>
+      <x:c r="B1490" t="str">
+        <x:v>41387432259100798</x:v>
+      </x:c>
+      <x:c r="C1490" t="str">
+        <x:v>공격태세+</x:v>
+      </x:c>
+      <x:c r="D1490" t="str">
+        <x:v>Attack Stance+</x:v>
+      </x:c>
+      <x:c r="E1490" t="str">
+        <x:v>攻击姿态+</x:v>
+      </x:c>
+      <x:c r="F1490" t="str">
+        <x:v>攻撃態勢+</x:v>
+      </x:c>
+      <x:c r="G1490" t="str">
+        <x:v>Postura de ataque+</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1491">
+      <x:c r="A1491" t="str">
+        <x:v>data.skill_master.s_core_64.tooltip</x:v>
+      </x:c>
+      <x:c r="B1491" t="str">
+        <x:v>41387432259100799</x:v>
+      </x:c>
+      <x:c r="C1491" t="str">
+        <x:v>자신과 아군에게 증폭 2를 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1491" t="str">
+        <x:v>Gives you and your allies Amplification 2.</x:v>
+      </x:c>
+      <x:c r="E1491" t="str">
+        <x:v>为你和你的盟友提供增幅 2。</x:v>
+      </x:c>
+      <x:c r="F1491" t="str">
+        <x:v>自分と味方に増幅2を与えます。</x:v>
+      </x:c>
+      <x:c r="G1491" t="str">
+        <x:v>Te da a ti y a tus aliados Amplificación 2.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1492">
+      <x:c r="A1492" t="str">
+        <x:v>data.skill_master.s_core_64.details</x:v>
+      </x:c>
+      <x:c r="B1492" t="str">
+        <x:v>41387432259100800</x:v>
+      </x:c>
+      <x:c r="C1492" t="str">
+        <x:v>자신과 아군에게 증폭 2 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1492" t="str">
+        <x:v>Gives amplification 2 to self and allies.</x:v>
+      </x:c>
+      <x:c r="E1492" t="str">
+        <x:v>给自己和盟友增幅2。</x:v>
+      </x:c>
+      <x:c r="F1492" t="str">
+        <x:v>自分と味方に増幅2を与えます。</x:v>
+      </x:c>
+      <x:c r="G1492" t="str">
+        <x:v>Otorga amplificación 2 a uno mismo y a sus aliados.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1493">
+      <x:c r="A1493" t="str">
+        <x:v>data.skill_master.s_core_65.name</x:v>
+      </x:c>
+      <x:c r="B1493" t="str">
+        <x:v>41387432259100801</x:v>
+      </x:c>
+      <x:c r="C1493" t="str">
+        <x:v>틈새베기</x:v>
+      </x:c>
+      <x:c r="D1493" t="str">
+        <x:v>Cut the gap</x:v>
+      </x:c>
+      <x:c r="E1493" t="str">
+        <x:v>缩小差距</x:v>
+      </x:c>
+      <x:c r="F1493" t="str">
+        <x:v>ニッチ</x:v>
+      </x:c>
+      <x:c r="G1493" t="str">
+        <x:v>Cortar la brecha</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1494">
+      <x:c r="A1494" t="str">
+        <x:v>data.skill_master.s_core_65.tooltip</x:v>
+      </x:c>
+      <x:c r="B1494" t="str">
+        <x:v>41387432259100802</x:v>
+      </x:c>
+      <x:c r="C1494" t="str">
+        <x:v>빠르게 베어 적에게 4의 피해를 줍니다.</x:v>
+      </x:c>
+      <x:c r="D1494" t="str">
+        <x:v>Quickly slashes, dealing 4 damage to the enemy.</x:v>
+      </x:c>
+      <x:c r="E1494" t="str">
+        <x:v>快速斩击，对敌人造成4点伤害。</x:v>
+      </x:c>
+      <x:c r="F1494" t="str">
+        <x:v>素早く斬り敵に4ダメージを与えます。</x:v>
+      </x:c>
+      <x:c r="G1494" t="str">
+        <x:v>Corta rápidamente, causando 4 daños al enemigo.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1495">
+      <x:c r="A1495" t="str">
+        <x:v>data.skill_master.s_core_65.details</x:v>
+      </x:c>
+      <x:c r="B1495" t="str">
+        <x:v>41387432259100803</x:v>
+      </x:c>
+      <x:c r="C1495" t="str">
+        <x:v>적에게 4의 피해를 줍니다.</x:v>
+      </x:c>
+      <x:c r="D1495" t="str">
+        <x:v>Deals 4 damage to the enemy.</x:v>
+      </x:c>
+      <x:c r="E1495" t="str">
+        <x:v>对敌人造成 4 点伤害。</x:v>
+      </x:c>
+      <x:c r="F1495" t="str">
+        <x:v>敵に4ダメージを与えます。</x:v>
+      </x:c>
+      <x:c r="G1495" t="str">
+        <x:v>Inflige 4 daños al enemigo.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1496">
+      <x:c r="A1496" t="str">
+        <x:v>data.skill_master.s_core_66.name</x:v>
+      </x:c>
+      <x:c r="B1496" t="str">
+        <x:v>41387432259100804</x:v>
+      </x:c>
+      <x:c r="C1496" t="str">
+        <x:v>틈새베기+</x:v>
+      </x:c>
+      <x:c r="D1496" t="str">
+        <x:v>Gap Cut+</x:v>
+      </x:c>
+      <x:c r="E1496" t="str">
+        <x:v>间隙切割+</x:v>
+      </x:c>
+      <x:c r="F1496" t="str">
+        <x:v>隙間斬り+</x:v>
+      </x:c>
+      <x:c r="G1496" t="str">
+        <x:v>Corte de espacio+</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1497">
+      <x:c r="A1497" t="str">
+        <x:v>data.skill_master.s_core_66.tooltip</x:v>
+      </x:c>
+      <x:c r="B1497" t="str">
+        <x:v>41387432259100805</x:v>
+      </x:c>
+      <x:c r="C1497" t="str">
+        <x:v>빠르게 베어 적에게 6의 피해를 줍니다.</x:v>
+      </x:c>
+      <x:c r="D1497" t="str">
+        <x:v>Quickly slashes to inflict 6 damage to the enemy.</x:v>
+      </x:c>
+      <x:c r="E1497" t="str">
+        <x:v>快速斩击，对敌人造成6点伤害。</x:v>
+      </x:c>
+      <x:c r="F1497" t="str">
+        <x:v>素早くクマ敵に6ダメージを与えます。</x:v>
+      </x:c>
+      <x:c r="G1497" t="str">
+        <x:v>Corta rápidamente para infligir 6 daños al enemigo.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1498">
+      <x:c r="A1498" t="str">
+        <x:v>data.skill_master.s_core_66.details</x:v>
+      </x:c>
+      <x:c r="B1498" t="str">
+        <x:v>41387432259100806</x:v>
+      </x:c>
+      <x:c r="C1498" t="str">
+        <x:v>적에게 6의 피해를 줍니다.</x:v>
+      </x:c>
+      <x:c r="D1498" t="str">
+        <x:v>Deals 6 damage to the enemy.</x:v>
+      </x:c>
+      <x:c r="E1498" t="str">
+        <x:v>对敌人造成 6 点伤害。</x:v>
+      </x:c>
+      <x:c r="F1498" t="str">
+        <x:v>敵に6のダメージを与えます。</x:v>
+      </x:c>
+      <x:c r="G1498" t="str">
+        <x:v>Inflige 6 daños al enemigo.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1499">
+      <x:c r="A1499" t="str">
+        <x:v>data.skill_master.s_core_67.name</x:v>
+      </x:c>
+      <x:c r="B1499" t="str">
+        <x:v>41387432259100807</x:v>
+      </x:c>
+      <x:c r="C1499" t="str">
+        <x:v>숨돌리기</x:v>
+      </x:c>
+      <x:c r="D1499" t="str">
+        <x:v>Take a breather</x:v>
+      </x:c>
+      <x:c r="E1499" t="str">
+        <x:v>喘口气</x:v>
+      </x:c>
+      <x:c r="F1499" t="str">
+        <x:v>隠す</x:v>
+      </x:c>
+      <x:c r="G1499" t="str">
+        <x:v>Toma un respiro</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1500">
+      <x:c r="A1500" t="str">
+        <x:v>data.skill_master.s_core_67.tooltip</x:v>
+      </x:c>
+      <x:c r="B1500" t="str">
+        <x:v>41387432259100808</x:v>
+      </x:c>
+      <x:c r="C1500" t="str">
+        <x:v>호흡을 가다듬어 자신에게 집중 1을 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1500" t="str">
+        <x:v>Take a deep breath and give yourself 1 focus.</x:v>
+      </x:c>
+      <x:c r="E1500" t="str">
+        <x:v>深吸一口气，给自己1个焦点。</x:v>
+      </x:c>
+      <x:c r="F1500" t="str">
+        <x:v>呼吸を練り、自分に集中1を与えます。</x:v>
+      </x:c>
+      <x:c r="G1500" t="str">
+        <x:v>Respira hondo y concéntrate en ti mismo.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1501">
+      <x:c r="A1501" t="str">
+        <x:v>data.skill_master.s_core_67.details</x:v>
+      </x:c>
+      <x:c r="B1501" t="str">
+        <x:v>41387432259100809</x:v>
+      </x:c>
+      <x:c r="C1501" t="str">
+        <x:v>자신에게 집중 1을 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1501" t="str">
+        <x:v>Gives you 1 focus.</x:v>
+      </x:c>
+      <x:c r="E1501" t="str">
+        <x:v>给你 1 个焦点。</x:v>
+      </x:c>
+      <x:c r="F1501" t="str">
+        <x:v>自分に集中1を与えます。</x:v>
+      </x:c>
+      <x:c r="G1501" t="str">
+        <x:v>Te da 1 enfoque.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1502">
+      <x:c r="A1502" t="str">
+        <x:v>data.skill_master.s_core_68.name</x:v>
+      </x:c>
+      <x:c r="B1502" t="str">
+        <x:v>41387432259100810</x:v>
+      </x:c>
+      <x:c r="C1502" t="str">
+        <x:v>숨돌리기+</x:v>
+      </x:c>
+      <x:c r="D1502" t="str">
+        <x:v>Take a breath+</x:v>
+      </x:c>
+      <x:c r="E1502" t="str">
+        <x:v>吸一口气+</x:v>
+      </x:c>
+      <x:c r="F1502" t="str">
+        <x:v>隠す+</x:v>
+      </x:c>
+      <x:c r="G1502" t="str">
+        <x:v>Toma un respiro+</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1503">
+      <x:c r="A1503" t="str">
+        <x:v>data.skill_master.s_core_68.tooltip</x:v>
+      </x:c>
+      <x:c r="B1503" t="str">
+        <x:v>41387432259100811</x:v>
+      </x:c>
+      <x:c r="C1503" t="str">
+        <x:v>호흡을 가다듬어 자신에게 집중 1을 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1503" t="str">
+        <x:v>Take a deep breath and give yourself 1 focus.</x:v>
+      </x:c>
+      <x:c r="E1503" t="str">
+        <x:v>深吸一口气，给自己1个焦点。</x:v>
+      </x:c>
+      <x:c r="F1503" t="str">
+        <x:v>呼吸を練り、自分に集中1を与えます。</x:v>
+      </x:c>
+      <x:c r="G1503" t="str">
+        <x:v>Respira hondo y concéntrate en ti mismo.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1504">
+      <x:c r="A1504" t="str">
+        <x:v>data.skill_master.s_core_68.details</x:v>
+      </x:c>
+      <x:c r="B1504" t="str">
+        <x:v>41387432259100812</x:v>
+      </x:c>
+      <x:c r="C1504" t="str">
+        <x:v>자신에게 집중 1을 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1504" t="str">
+        <x:v>Gives you 1 focus.</x:v>
+      </x:c>
+      <x:c r="E1504" t="str">
+        <x:v>给你 1 个焦点。</x:v>
+      </x:c>
+      <x:c r="F1504" t="str">
+        <x:v>自分に集中1を与えます。</x:v>
+      </x:c>
+      <x:c r="G1504" t="str">
+        <x:v>Te da 1 enfoque.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1505">
+      <x:c r="A1505" t="str">
+        <x:v>data.skill_master.s_core_69.name</x:v>
+      </x:c>
+      <x:c r="B1505" t="str">
+        <x:v>41387432259100813</x:v>
+      </x:c>
+      <x:c r="C1505" t="str">
+        <x:v>밀쳐내기</x:v>
+      </x:c>
+      <x:c r="D1505" t="str">
+        <x:v>Push</x:v>
+      </x:c>
+      <x:c r="E1505" t="str">
+        <x:v>推</x:v>
+      </x:c>
+      <x:c r="F1505" t="str">
+        <x:v>押し出す</x:v>
+      </x:c>
+      <x:c r="G1505" t="str">
+        <x:v>Empujar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1506">
+      <x:c r="A1506" t="str">
+        <x:v>data.skill_master.s_core_69.tooltip</x:v>
+      </x:c>
+      <x:c r="B1506" t="str">
+        <x:v>41387432259100814</x:v>
+      </x:c>
+      <x:c r="C1506" t="str">
+        <x:v>몸으로 밀쳐 적에게 4의 피해를 주고 1칸 밀쳐냅니다.</x:v>
+      </x:c>
+      <x:c r="D1506" t="str">
+        <x:v>Push back with your body, dealing 4 damage to the enemy and pushing them back 1 space.</x:v>
+      </x:c>
+      <x:c r="E1506" t="str">
+        <x:v>用身体向后推，对敌人造成4点伤害，并将其推开1格。</x:v>
+      </x:c>
+      <x:c r="F1506" t="str">
+        <x:v>体で押して敵に4のダメージを与えて1マス押し出します。</x:v>
+      </x:c>
+      <x:c r="G1506" t="str">
+        <x:v>Empuja hacia atrás con tu cuerpo, causando 4 daños al enemigo y empujándolo hacia atrás 1 espacio.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1507">
+      <x:c r="A1507" t="str">
+        <x:v>data.skill_master.s_core_69.details</x:v>
+      </x:c>
+      <x:c r="B1507" t="str">
+        <x:v>41387432259100815</x:v>
+      </x:c>
+      <x:c r="C1507" t="str">
+        <x:v>적에게 4의 피해를 줍니다. 1칸 밀쳐냅니다.</x:v>
+      </x:c>
+      <x:c r="D1507" t="str">
+        <x:v>Deals 4 damage to the enemy. Pushes 1 space.</x:v>
+      </x:c>
+      <x:c r="E1507" t="str">
+        <x:v>对敌人造成 4 点伤害。推1个空格。</x:v>
+      </x:c>
+      <x:c r="F1507" t="str">
+        <x:v>敵に4ダメージを与えます。 1マス押し出します。</x:v>
+      </x:c>
+      <x:c r="G1507" t="str">
+        <x:v>Inflige 4 daños al enemigo. Empuja 1 espacio.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1508">
+      <x:c r="A1508" t="str">
+        <x:v>data.skill_master.s_core_70.name</x:v>
+      </x:c>
+      <x:c r="B1508" t="str">
+        <x:v>41387432259100816</x:v>
+      </x:c>
+      <x:c r="C1508" t="str">
+        <x:v>밀쳐내기+</x:v>
+      </x:c>
+      <x:c r="D1508" t="str">
+        <x:v>Push+</x:v>
+      </x:c>
+      <x:c r="E1508" t="str">
+        <x:v>推+</x:v>
+      </x:c>
+      <x:c r="F1508" t="str">
+        <x:v>押し出す+</x:v>
+      </x:c>
+      <x:c r="G1508" t="str">
+        <x:v>Empujar+</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1509">
+      <x:c r="A1509" t="str">
+        <x:v>data.skill_master.s_core_70.tooltip</x:v>
+      </x:c>
+      <x:c r="B1509" t="str">
+        <x:v>41387432259100817</x:v>
+      </x:c>
+      <x:c r="C1509" t="str">
+        <x:v>몸으로 밀쳐 적에게 4의 피해를 주고 1칸 밀쳐냅니다.</x:v>
+      </x:c>
+      <x:c r="D1509" t="str">
+        <x:v>Push back with your body, dealing 4 damage to the enemy and pushing them back 1 space.</x:v>
+      </x:c>
+      <x:c r="E1509" t="str">
+        <x:v>用身体向后推，对敌人造成4点伤害，并将其推开1格。</x:v>
+      </x:c>
+      <x:c r="F1509" t="str">
+        <x:v>体で押して敵に4のダメージを与えて1マス押し出します。</x:v>
+      </x:c>
+      <x:c r="G1509" t="str">
+        <x:v>Empuja hacia atrás con tu cuerpo, causando 4 daños al enemigo y empujándolo hacia atrás 1 espacio.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1510">
+      <x:c r="A1510" t="str">
+        <x:v>data.skill_master.s_core_70.details</x:v>
+      </x:c>
+      <x:c r="B1510" t="str">
+        <x:v>41387432259100818</x:v>
+      </x:c>
+      <x:c r="C1510" t="str">
+        <x:v>적에게 4의 피해를 줍니다. 1칸 밀쳐냅니다.</x:v>
+      </x:c>
+      <x:c r="D1510" t="str">
+        <x:v>Deals 4 damage to the enemy. Pushes 1 space.</x:v>
+      </x:c>
+      <x:c r="E1510" t="str">
+        <x:v>对敌人造成 4 点伤害。推1个空格。</x:v>
+      </x:c>
+      <x:c r="F1510" t="str">
+        <x:v>敵に4ダメージを与えます。 1マス押し出します。</x:v>
+      </x:c>
+      <x:c r="G1510" t="str">
+        <x:v>Inflige 4 daños al enemigo. Empuja 1 espacio.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1511">
+      <x:c r="A1511" t="str">
+        <x:v>data.skill_master.s_core_71.name</x:v>
+      </x:c>
+      <x:c r="B1511" t="str">
+        <x:v>41387432259100819</x:v>
+      </x:c>
+      <x:c r="C1511" t="str">
+        <x:v>격려</x:v>
+      </x:c>
+      <x:c r="D1511" t="str">
+        <x:v>Encouragement</x:v>
+      </x:c>
+      <x:c r="E1511" t="str">
+        <x:v>鼓舞</x:v>
+      </x:c>
+      <x:c r="F1511" t="str">
+        <x:v>激励</x:v>
+      </x:c>
+      <x:c r="G1511" t="str">
+        <x:v>Ánimo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1512">
+      <x:c r="A1512" t="str">
+        <x:v>data.skill_master.s_core_71.tooltip</x:v>
+      </x:c>
+      <x:c r="B1512" t="str">
+        <x:v>41387432259100820</x:v>
+      </x:c>
+      <x:c r="C1512" t="str">
+        <x:v>용기를 북돋아 아군에게 충전 2를 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1512" t="str">
+        <x:v>Inspires courage and grants 2 charges to an ally.</x:v>
+      </x:c>
+      <x:c r="E1512" t="str">
+        <x:v>激发勇气并为盟友提供 2 次冲锋。</x:v>
+      </x:c>
+      <x:c r="F1512" t="str">
+        <x:v>勇気を盛り上げて味方にチャージ2を与えます。</x:v>
+      </x:c>
+      <x:c r="G1512" t="str">
+        <x:v>Inspira coraje y otorga 2 cargas a un aliado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1513">
+      <x:c r="A1513" t="str">
+        <x:v>data.skill_master.s_core_71.details</x:v>
+      </x:c>
+      <x:c r="B1513" t="str">
+        <x:v>41387432259100821</x:v>
+      </x:c>
+      <x:c r="C1513" t="str">
+        <x:v>아군에게 충전 2를 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1513" t="str">
+        <x:v>Gives 2 charges to an ally.</x:v>
+      </x:c>
+      <x:c r="E1513" t="str">
+        <x:v>为盟友提供 2 点费用。</x:v>
+      </x:c>
+      <x:c r="F1513" t="str">
+        <x:v>味方にチャージ2を与えます。</x:v>
+      </x:c>
+      <x:c r="G1513" t="str">
+        <x:v>Otorga 2 cargas a un aliado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1514">
+      <x:c r="A1514" t="str">
+        <x:v>data.skill_master.s_core_72.name</x:v>
+      </x:c>
+      <x:c r="B1514" t="str">
+        <x:v>41387432259100822</x:v>
+      </x:c>
+      <x:c r="C1514" t="str">
+        <x:v>격려+</x:v>
+      </x:c>
+      <x:c r="D1514" t="str">
+        <x:v>격려+</x:v>
+      </x:c>
+      <x:c r="E1514" t="str">
+        <x:v>격려+</x:v>
+      </x:c>
+      <x:c r="F1514" t="str">
+        <x:v>격려+</x:v>
+      </x:c>
+      <x:c r="G1514" t="str">
+        <x:v>격려+</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1515">
+      <x:c r="A1515" t="str">
+        <x:v>data.skill_master.s_core_72.tooltip</x:v>
+      </x:c>
+      <x:c r="B1515" t="str">
+        <x:v>41387432259100823</x:v>
+      </x:c>
+      <x:c r="C1515" t="str">
+        <x:v>용기를 북돋아 아군에게 충전 2를 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1515" t="str">
+        <x:v>Inspires courage and grants 2 charges to an ally.</x:v>
+      </x:c>
+      <x:c r="E1515" t="str">
+        <x:v>激发勇气并为盟友提供 2 次冲锋。</x:v>
+      </x:c>
+      <x:c r="F1515" t="str">
+        <x:v>勇気を盛り上げて味方にチャージ2を与えます。</x:v>
+      </x:c>
+      <x:c r="G1515" t="str">
+        <x:v>Inspira coraje y otorga 2 cargas a un aliado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1516">
+      <x:c r="A1516" t="str">
+        <x:v>data.skill_master.s_core_72.details</x:v>
+      </x:c>
+      <x:c r="B1516" t="str">
+        <x:v>41387432259100824</x:v>
+      </x:c>
+      <x:c r="C1516" t="str">
+        <x:v>아군에게 충전 2를 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1516" t="str">
+        <x:v>Gives 2 charges to an ally.</x:v>
+      </x:c>
+      <x:c r="E1516" t="str">
+        <x:v>为盟友提供 2 点费用。</x:v>
+      </x:c>
+      <x:c r="F1516" t="str">
+        <x:v>味方にチャージ2を与えます。</x:v>
+      </x:c>
+      <x:c r="G1516" t="str">
+        <x:v>Otorga 2 cargas a un aliado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1517">
+      <x:c r="A1517" t="str">
+        <x:v>data.skill_master.s_core_73.name</x:v>
+      </x:c>
+      <x:c r="B1517" t="str">
+        <x:v>41387432259100825</x:v>
+      </x:c>
+      <x:c r="C1517" t="str">
+        <x:v>버티기</x:v>
+      </x:c>
+      <x:c r="D1517" t="str">
+        <x:v>Hold on</x:v>
+      </x:c>
+      <x:c r="E1517" t="str">
+        <x:v>等等</x:v>
+      </x:c>
+      <x:c r="F1517" t="str">
+        <x:v>バティ</x:v>
+      </x:c>
+      <x:c r="G1517" t="str">
+        <x:v>Espera</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1518">
+      <x:c r="A1518" t="str">
+        <x:v>data.skill_master.s_core_73.tooltip</x:v>
+      </x:c>
+      <x:c r="B1518" t="str">
+        <x:v>41387432259100826</x:v>
+      </x:c>
+      <x:c r="C1518" t="str">
+        <x:v>굳게 버텨 자신과 아군에게 방어도 4를 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1518" t="str">
+        <x:v>Stand firm and grant 4 armor to yourself and your allies.</x:v>
+      </x:c>
+      <x:c r="E1518" t="str">
+        <x:v>坚定立场，为自己和盟友提供 4 点护甲。</x:v>
+      </x:c>
+      <x:c r="F1518" t="str">
+        <x:v>頑固に自分自身と味方に防御も4を付与します。</x:v>
+      </x:c>
+      <x:c r="G1518" t="str">
+        <x:v>Mantente firme y otorga 4 armaduras para ti y tus aliados.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1519">
+      <x:c r="A1519" t="str">
+        <x:v>data.skill_master.s_core_73.details</x:v>
+      </x:c>
+      <x:c r="B1519" t="str">
+        <x:v>41387432259100827</x:v>
+      </x:c>
+      <x:c r="C1519" t="str">
+        <x:v>자신과 아군에게 방어도 4를 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1519" t="str">
+        <x:v>Grants 4 armor to you and your allies.</x:v>
+      </x:c>
+      <x:c r="E1519" t="str">
+        <x:v>为你和你的盟友提供 4 点护甲。</x:v>
+      </x:c>
+      <x:c r="F1519" t="str">
+        <x:v>自分と味方に防御も4を与えます。</x:v>
+      </x:c>
+      <x:c r="G1519" t="str">
+        <x:v>Te otorga 4 armaduras a ti y a tus aliados.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1520">
+      <x:c r="A1520" t="str">
+        <x:v>data.skill_master.s_core_74.name</x:v>
+      </x:c>
+      <x:c r="B1520" t="str">
+        <x:v>41387432259100828</x:v>
+      </x:c>
+      <x:c r="C1520" t="str">
+        <x:v>버티기+</x:v>
+      </x:c>
+      <x:c r="D1520" t="str">
+        <x:v>Hold on+</x:v>
+      </x:c>
+      <x:c r="E1520" t="str">
+        <x:v>坚持+</x:v>
+      </x:c>
+      <x:c r="F1520" t="str">
+        <x:v>バティ+</x:v>
+      </x:c>
+      <x:c r="G1520" t="str">
+        <x:v>Espera+</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1521">
+      <x:c r="A1521" t="str">
+        <x:v>data.skill_master.s_core_74.tooltip</x:v>
+      </x:c>
+      <x:c r="B1521" t="str">
+        <x:v>41387432259100829</x:v>
+      </x:c>
+      <x:c r="C1521" t="str">
+        <x:v>굳게 버텨 자신과 아군에게 방어도 4를 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1521" t="str">
+        <x:v>Stand firm and grant 4 armor to yourself and your allies.</x:v>
+      </x:c>
+      <x:c r="E1521" t="str">
+        <x:v>坚定立场，为自己和盟友提供 4 点护甲。</x:v>
+      </x:c>
+      <x:c r="F1521" t="str">
+        <x:v>頑固に自分自身と味方に防御も4を付与します。</x:v>
+      </x:c>
+      <x:c r="G1521" t="str">
+        <x:v>Mantente firme y otorga 4 armaduras para ti y tus aliados.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1522">
+      <x:c r="A1522" t="str">
+        <x:v>data.skill_master.s_core_74.details</x:v>
+      </x:c>
+      <x:c r="B1522" t="str">
+        <x:v>41387432259100830</x:v>
+      </x:c>
+      <x:c r="C1522" t="str">
+        <x:v>자신과 아군에게 방어도 4를 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1522" t="str">
+        <x:v>Grants 4 armor to you and your allies.</x:v>
+      </x:c>
+      <x:c r="E1522" t="str">
+        <x:v>为你和你的盟友提供 4 点护甲。</x:v>
+      </x:c>
+      <x:c r="F1522" t="str">
+        <x:v>自分と味方に防御も4を与えます。</x:v>
+      </x:c>
+      <x:c r="G1522" t="str">
+        <x:v>Te otorga 4 armaduras a ti y a tus aliados.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1523">
+      <x:c r="A1523" t="str">
+        <x:v>data.skill_master.s_core_75.name</x:v>
+      </x:c>
+      <x:c r="B1523" t="str">
+        <x:v>41387432259100831</x:v>
+      </x:c>
+      <x:c r="C1523" t="str">
+        <x:v>끌어당기기</x:v>
+      </x:c>
+      <x:c r="D1523" t="str">
+        <x:v>Pull</x:v>
+      </x:c>
+      <x:c r="E1523" t="str">
+        <x:v>拉</x:v>
+      </x:c>
+      <x:c r="F1523" t="str">
+        <x:v>ドラッグ</x:v>
+      </x:c>
+      <x:c r="G1523" t="str">
+        <x:v>Tirar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1524">
+      <x:c r="A1524" t="str">
+        <x:v>data.skill_master.s_core_75.tooltip</x:v>
+      </x:c>
+      <x:c r="B1524" t="str">
+        <x:v>41387432259100832</x:v>
+      </x:c>
+      <x:c r="C1524" t="str">
+        <x:v>적을 붙잡아 끌어당기며 4의 피해를 줍니다.</x:v>
+      </x:c>
+      <x:c r="D1524" t="str">
+        <x:v>Grabs the enemy and pulls it in, dealing 4 damage.</x:v>
+      </x:c>
+      <x:c r="E1524" t="str">
+        <x:v>抓住敌人并将其拉入，造成 4 点伤害。</x:v>
+      </x:c>
+      <x:c r="F1524" t="str">
+        <x:v>敵を捕まえて引っ張って4ダメージを与えます。</x:v>
+      </x:c>
+      <x:c r="G1524" t="str">
+        <x:v>Agarra al enemigo y lo atrae, causándole 4 daños.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1525">
+      <x:c r="A1525" t="str">
+        <x:v>data.skill_master.s_core_75.details</x:v>
+      </x:c>
+      <x:c r="B1525" t="str">
+        <x:v>41387432259100833</x:v>
+      </x:c>
+      <x:c r="C1525" t="str">
+        <x:v>적에게 5의 피해를 줍니다. 1칸 당겨옵니다.</x:v>
+      </x:c>
+      <x:c r="D1525" t="str">
+        <x:v>Deals 5 damage to the enemy. Pull 1 space.</x:v>
+      </x:c>
+      <x:c r="E1525" t="str">
+        <x:v>对敌人造成 5 点伤害。拉1个空格。</x:v>
+      </x:c>
+      <x:c r="F1525" t="str">
+        <x:v>敵に5ダメージを与えます。 1マス引きます。</x:v>
+      </x:c>
+      <x:c r="G1525" t="str">
+        <x:v>Inflige 5 daños al enemigo. Tira 1 espacio.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1526">
+      <x:c r="A1526" t="str">
+        <x:v>data.skill_master.s_core_76.name</x:v>
+      </x:c>
+      <x:c r="B1526" t="str">
+        <x:v>41387432259100834</x:v>
+      </x:c>
+      <x:c r="C1526" t="str">
+        <x:v>끌어당기기+</x:v>
+      </x:c>
+      <x:c r="D1526" t="str">
+        <x:v>Pull+</x:v>
+      </x:c>
+      <x:c r="E1526" t="str">
+        <x:v>拉+</x:v>
+      </x:c>
+      <x:c r="F1526" t="str">
+        <x:v>プル+</x:v>
+      </x:c>
+      <x:c r="G1526" t="str">
+        <x:v>Tirar+</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1527">
+      <x:c r="A1527" t="str">
+        <x:v>data.skill_master.s_core_76.tooltip</x:v>
+      </x:c>
+      <x:c r="B1527" t="str">
+        <x:v>41387432259100835</x:v>
+      </x:c>
+      <x:c r="C1527" t="str">
+        <x:v>적을 붙잡아 끌어당기며 6의 피해를 줍니다.</x:v>
+      </x:c>
+      <x:c r="D1527" t="str">
+        <x:v>Grabs the enemy and pulls it in, dealing 6 damage.</x:v>
+      </x:c>
+      <x:c r="E1527" t="str">
+        <x:v>抓住敌人并将其拉入，造成 6 点伤害。</x:v>
+      </x:c>
+      <x:c r="F1527" t="str">
+        <x:v>敵を捕まえて引っ張って6のダメージを与えます。</x:v>
+      </x:c>
+      <x:c r="G1527" t="str">
+        <x:v>Agarra al enemigo y lo atrae, causándole 6 daños.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1528">
+      <x:c r="A1528" t="str">
+        <x:v>data.skill_master.s_core_76.details</x:v>
+      </x:c>
+      <x:c r="B1528" t="str">
+        <x:v>41387432259100836</x:v>
+      </x:c>
+      <x:c r="C1528" t="str">
+        <x:v>적에게 6의 피해를 줍니다. 1칸 당겨옵니다.</x:v>
+      </x:c>
+      <x:c r="D1528" t="str">
+        <x:v>Deals 6 damage to the enemy. Pull 1 space.</x:v>
+      </x:c>
+      <x:c r="E1528" t="str">
+        <x:v>对敌人造成 6 点伤害。拉1个空格。</x:v>
+      </x:c>
+      <x:c r="F1528" t="str">
+        <x:v>敵に6のダメージを与えます。 1マス引きます。</x:v>
+      </x:c>
+      <x:c r="G1528" t="str">
+        <x:v>Inflige 6 daños al enemigo. Tira 1 espacio.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1529">
+      <x:c r="A1529" t="str">
+        <x:v>data.skill_master.s_core_77.name</x:v>
+      </x:c>
+      <x:c r="B1529" t="str">
+        <x:v>41387432259100837</x:v>
+      </x:c>
+      <x:c r="C1529" t="str">
+        <x:v>블러드피어스</x:v>
+      </x:c>
+      <x:c r="D1529" t="str">
+        <x:v>Bloodpierce</x:v>
+      </x:c>
+      <x:c r="E1529" t="str">
+        <x:v>血刺</x:v>
+      </x:c>
+      <x:c r="F1529" t="str">
+        <x:v>ブラッドピアス</x:v>
+      </x:c>
+      <x:c r="G1529" t="str">
+        <x:v>Perforador de sangre</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1530">
+      <x:c r="A1530" t="str">
+        <x:v>data.skill_master.s_core_77.tooltip</x:v>
+      </x:c>
+      <x:c r="B1530" t="str">
+        <x:v>41387432259100838</x:v>
+      </x:c>
+      <x:c r="C1530" t="str">
+        <x:v>적을 찔러 4의 피해를 주고 출혈 1을 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1530" t="str">
+        <x:v>Stab the enemy, dealing 4 damage and inflicting 1 bleeding.</x:v>
+      </x:c>
+      <x:c r="E1530" t="str">
+        <x:v>刺刺敌人，造成4点伤害并造成1点出血。</x:v>
+      </x:c>
+      <x:c r="F1530" t="str">
+        <x:v>敵を突き刺し、4のダメージを与え、出血1を与える。</x:v>
+      </x:c>
+      <x:c r="G1530" t="str">
+        <x:v>Apuñala al enemigo, causando 4 daños e infligiendo 1 sangrado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1531">
+      <x:c r="A1531" t="str">
+        <x:v>data.skill_master.s_core_77.details</x:v>
+      </x:c>
+      <x:c r="B1531" t="str">
+        <x:v>41387432259100839</x:v>
+      </x:c>
+      <x:c r="C1531" t="str">
+        <x:v>적에게 4의 피해를 줍니다. 출혈 1을 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1531" t="str">
+        <x:v>Deals 4 damage to the enemy. Grants 1 bleeding.</x:v>
+      </x:c>
+      <x:c r="E1531" t="str">
+        <x:v>对敌人造成 4 点伤害。给予 1 次出血。</x:v>
+      </x:c>
+      <x:c r="F1531" t="str">
+        <x:v>敵に4ダメージを与えます。出血1を与えます。</x:v>
+      </x:c>
+      <x:c r="G1531" t="str">
+        <x:v>Inflige 4 daños al enemigo. Otorga 1 sangrado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1532">
+      <x:c r="A1532" t="str">
+        <x:v>data.skill_master.s_core_78.name</x:v>
+      </x:c>
+      <x:c r="B1532" t="str">
+        <x:v>41387432259100840</x:v>
+      </x:c>
+      <x:c r="C1532" t="str">
+        <x:v>블러드피어스+</x:v>
+      </x:c>
+      <x:c r="D1532" t="str">
+        <x:v>Bloodpierce+</x:v>
+      </x:c>
+      <x:c r="E1532" t="str">
+        <x:v>血刺+</x:v>
+      </x:c>
+      <x:c r="F1532" t="str">
+        <x:v>ブラッドピアス+</x:v>
+      </x:c>
+      <x:c r="G1532" t="str">
+        <x:v>Perforación de sangre+</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1533">
+      <x:c r="A1533" t="str">
+        <x:v>data.skill_master.s_core_78.tooltip</x:v>
+      </x:c>
+      <x:c r="B1533" t="str">
+        <x:v>41387432259100841</x:v>
+      </x:c>
+      <x:c r="C1533" t="str">
+        <x:v>적을 찔러 4의 피해를 주고 출혈 1을 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1533" t="str">
+        <x:v>Stab the enemy, dealing 4 damage and inflicting 1 bleeding.</x:v>
+      </x:c>
+      <x:c r="E1533" t="str">
+        <x:v>刺刺敌人，造成4点伤害并造成1点出血。</x:v>
+      </x:c>
+      <x:c r="F1533" t="str">
+        <x:v>敵を突き刺し、4のダメージを与え、出血1を与える。</x:v>
+      </x:c>
+      <x:c r="G1533" t="str">
+        <x:v>Apuñala al enemigo, causando 4 daños e infligiendo 1 sangrado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1534">
+      <x:c r="A1534" t="str">
+        <x:v>data.skill_master.s_core_78.details</x:v>
+      </x:c>
+      <x:c r="B1534" t="str">
+        <x:v>41387432259100842</x:v>
+      </x:c>
+      <x:c r="C1534" t="str">
+        <x:v>적에게 4의 피해를 줍니다. 출혈 1을 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1534" t="str">
+        <x:v>Deals 4 damage to the enemy. Grants 1 bleeding.</x:v>
+      </x:c>
+      <x:c r="E1534" t="str">
+        <x:v>对敌人造成 4 点伤害。给予 1 次出血。</x:v>
+      </x:c>
+      <x:c r="F1534" t="str">
+        <x:v>敵に4ダメージを与えます。出血1を与えます。</x:v>
+      </x:c>
+      <x:c r="G1534" t="str">
+        <x:v>Inflige 4 daños al enemigo. Otorga 1 sangrado.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1535">
+      <x:c r="A1535" t="str">
+        <x:v>data.skill_master.s_core_79.name</x:v>
+      </x:c>
+      <x:c r="B1535" t="str">
+        <x:v>41387432259100843</x:v>
+      </x:c>
+      <x:c r="C1535" t="str">
+        <x:v>스피드스터</x:v>
+      </x:c>
+      <x:c r="D1535" t="str">
+        <x:v>Speedster</x:v>
+      </x:c>
+      <x:c r="E1535" t="str">
+        <x:v>极速者</x:v>
+      </x:c>
+      <x:c r="F1535" t="str">
+        <x:v>スピードスター</x:v>
+      </x:c>
+      <x:c r="G1535" t="str">
+        <x:v>Velocista</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1536">
+      <x:c r="A1536" t="str">
+        <x:v>data.skill_master.s_core_79.tooltip</x:v>
+      </x:c>
+      <x:c r="B1536" t="str">
+        <x:v>41387432259100844</x:v>
+      </x:c>
+      <x:c r="C1536" t="str">
+        <x:v>상대보다 먼저 움직일 틈을 잡아 신속 1을 얻습니다.</x:v>
+      </x:c>
+      <x:c r="D1536" t="str">
+        <x:v>Seize the opportunity to move before your opponent and gain 1 speed.</x:v>
+      </x:c>
+      <x:c r="E1536" t="str">
+        <x:v>抓住机会在对手之前移动并获得 1 点速度。</x:v>
+      </x:c>
+      <x:c r="F1536" t="str">
+        <x:v>相手より先に移動するギャップをつかみ、速い1を得る。</x:v>
+      </x:c>
+      <x:c r="G1536" t="str">
+        <x:v>Aprovecha la oportunidad para moverte antes que tu oponente y ganar 1 velocidad.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1537">
+      <x:c r="A1537" t="str">
+        <x:v>data.skill_master.s_core_79.details</x:v>
+      </x:c>
+      <x:c r="B1537" t="str">
+        <x:v>41387432259100845</x:v>
+      </x:c>
+      <x:c r="C1537" t="str">
+        <x:v>자신에게 신속 1을 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1537" t="str">
+        <x:v>Gives yourself speed 1.</x:v>
+      </x:c>
+      <x:c r="E1537" t="str">
+        <x:v>给自己速度 1。</x:v>
+      </x:c>
+      <x:c r="F1537" t="str">
+        <x:v>自分に素早く1を与えます。</x:v>
+      </x:c>
+      <x:c r="G1537" t="str">
+        <x:v>Te da velocidad 1.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1538">
+      <x:c r="A1538" t="str">
+        <x:v>data.skill_master.s_core_80.name</x:v>
+      </x:c>
+      <x:c r="B1538" t="str">
+        <x:v>41387432259100846</x:v>
+      </x:c>
+      <x:c r="C1538" t="str">
+        <x:v>스피드스터+</x:v>
+      </x:c>
+      <x:c r="D1538" t="str">
+        <x:v>Speedster+</x:v>
+      </x:c>
+      <x:c r="E1538" t="str">
+        <x:v>极速+</x:v>
+      </x:c>
+      <x:c r="F1538" t="str">
+        <x:v>スピードスター+</x:v>
+      </x:c>
+      <x:c r="G1538" t="str">
+        <x:v>Velocista+</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1539">
+      <x:c r="A1539" t="str">
+        <x:v>data.skill_master.s_core_80.tooltip</x:v>
+      </x:c>
+      <x:c r="B1539" t="str">
+        <x:v>41387432259100847</x:v>
+      </x:c>
+      <x:c r="C1539" t="str">
+        <x:v>상대보다 먼저 움직일 틈을 잡아 신속 1을 얻습니다.</x:v>
+      </x:c>
+      <x:c r="D1539" t="str">
+        <x:v>Seize the opportunity to move before your opponent and gain 1 speed.</x:v>
+      </x:c>
+      <x:c r="E1539" t="str">
+        <x:v>抓住机会在对手之前移动并获得 1 点速度。</x:v>
+      </x:c>
+      <x:c r="F1539" t="str">
+        <x:v>相手より先に移動するギャップをつかみ、速い1を得る。</x:v>
+      </x:c>
+      <x:c r="G1539" t="str">
+        <x:v>Aprovecha la oportunidad para moverte antes que tu oponente y ganar 1 velocidad.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1540">
+      <x:c r="A1540" t="str">
+        <x:v>data.skill_master.s_core_80.details</x:v>
+      </x:c>
+      <x:c r="B1540" t="str">
+        <x:v>41387432259100848</x:v>
+      </x:c>
+      <x:c r="C1540" t="str">
+        <x:v>자신에게 신속 1을 부여합니다.</x:v>
+      </x:c>
+      <x:c r="D1540" t="str">
+        <x:v>Gives yourself speed 1.</x:v>
+      </x:c>
+      <x:c r="E1540" t="str">
+        <x:v>给自己速度 1。</x:v>
+      </x:c>
+      <x:c r="F1540" t="str">
+        <x:v>自分に素早く1を与えます。</x:v>
+      </x:c>
+      <x:c r="G1540" t="str">
+        <x:v>Te da velocidad 1.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1541">
+      <x:c r="A1541" t="str">
+        <x:v>lobby.trial.unlock.stage3_clear</x:v>
+      </x:c>
+      <x:c r="B1541" t="str">
+        <x:v>41387432259100849</x:v>
+      </x:c>
+      <x:c r="C1541" t="str">
+        <x:v>해금 : 3구역 1회 클리어</x:v>
+      </x:c>
+      <x:c r="D1541" t="str">
+        <x:v>Unlock: Clear Area 3 once.</x:v>
+      </x:c>
+      <x:c r="E1541" t="str">
+        <x:v>解锁：通关第3区域1次。</x:v>
+      </x:c>
+      <x:c r="F1541" t="str">
+        <x:v>解放：エリア3を1回クリア</x:v>
+      </x:c>
+      <x:c r="G1541" t="str">
+        <x:v>Desbloqueo: despeja el Área 3 una vez.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1542">
+      <x:c r="A1542" t="str">
+        <x:v>lobby.trial.unlock.nocturne_kill</x:v>
+      </x:c>
+      <x:c r="B1542" t="str">
+        <x:v>41387432259100850</x:v>
+      </x:c>
+      <x:c r="C1542" t="str">
+        <x:v>해금 : 녹턴 3회 처치</x:v>
+      </x:c>
+      <x:c r="D1542" t="str">
+        <x:v>Unlock: Defeat Nocturne 3 times.</x:v>
+      </x:c>
+      <x:c r="E1542" t="str">
+        <x:v>解锁：击败夜曲3次。</x:v>
+      </x:c>
+      <x:c r="F1542" t="str">
+        <x:v>解放：ノクトンを3回撃破</x:v>
+      </x:c>
+      <x:c r="G1542" t="str">
+        <x:v>Desbloqueo: derrota a Nocturno 3 veces.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="1543">
+      <x:c r="A1543" t="str">
+        <x:v>lobby.trial.unlock.two_trials_clear</x:v>
+      </x:c>
+      <x:c r="B1543" t="str">
+        <x:v>41387432259100851</x:v>
+      </x:c>
+      <x:c r="C1543" t="str">
+        <x:v>해금 : 2개의 시련을 적용 후 클리어</x:v>
+      </x:c>
+      <x:c r="D1543" t="str">
+        <x:v>Unlock: Clear with 2 Trials applied.</x:v>
+      </x:c>
+      <x:c r="E1543" t="str">
+        <x:v>解锁：应用2个试炼后通关。</x:v>
+      </x:c>
+      <x:c r="F1543" t="str">
+        <x:v>解放：2つの試練を適用してクリア</x:v>
+      </x:c>
+      <x:c r="G1543" t="str">
+        <x:v>Desbloqueo: completa con 2 pruebas aplicadas.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
